--- a/12626877.xlsx
+++ b/12626877.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8ce47a147eef90b5/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="259" documentId="13_ncr:1_{B2656224-C1C2-42E6-AA6E-541CE199D262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEC7214E-4734-43D9-B939-CC8D716D13AD}"/>
+  <xr:revisionPtr revIDLastSave="313" documentId="13_ncr:1_{B2656224-C1C2-42E6-AA6E-541CE199D262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CFFED10-431F-4050-AD5C-B9B81A60FD1A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -266,6 +266,18 @@
   </si>
   <si>
     <t>Busy Day.</t>
+  </si>
+  <si>
+    <t>Attended classes and learned topics.</t>
+  </si>
+  <si>
+    <t>Completed today's tasks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> It was a hectic day.</t>
+  </si>
+  <si>
+    <t>good day.</t>
   </si>
 </sst>
 </file>
@@ -2301,10 +2313,10 @@
         <v>60</v>
       </c>
       <c r="D33" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E33" s="14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F33" s="14">
         <v>350</v>
@@ -2317,11 +2329,11 @@
       </c>
       <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v>980</v>
+        <v>1010</v>
       </c>
       <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v>460</v>
+        <v>430</v>
       </c>
       <c r="K33" s="16" t="s">
         <v>57</v>
@@ -2382,181 +2394,373 @@
         <v>76</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+    <row r="35" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A35" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B35" s="14">
+        <v>420</v>
+      </c>
+      <c r="C35" s="14">
+        <v>60</v>
+      </c>
+      <c r="D35" s="14">
+        <v>60</v>
+      </c>
+      <c r="E35" s="14">
+        <v>15</v>
+      </c>
+      <c r="F35" s="14">
+        <v>350</v>
+      </c>
+      <c r="G35" s="14">
+        <v>7</v>
+      </c>
+      <c r="H35" s="14">
+        <v>60</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>965</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>475</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B36" s="14">
+        <v>420</v>
+      </c>
+      <c r="C36" s="14">
+        <v>60</v>
+      </c>
+      <c r="D36" s="14">
+        <v>60</v>
+      </c>
+      <c r="E36" s="14">
+        <v>30</v>
+      </c>
+      <c r="F36" s="14">
+        <v>100</v>
+      </c>
+      <c r="G36" s="14">
+        <v>2</v>
+      </c>
+      <c r="H36" s="14">
+        <v>60</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>730</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>710</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B37" s="14">
+        <v>420</v>
+      </c>
+      <c r="C37" s="14">
+        <v>60</v>
+      </c>
+      <c r="D37" s="14">
+        <v>60</v>
+      </c>
+      <c r="E37" s="14">
+        <v>30</v>
+      </c>
+      <c r="F37" s="14">
+        <v>100</v>
+      </c>
+      <c r="G37" s="14">
+        <v>2</v>
+      </c>
+      <c r="H37" s="14">
+        <v>60</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>730</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>710</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B38" s="14">
+        <v>420</v>
+      </c>
+      <c r="C38" s="14">
+        <v>60</v>
+      </c>
+      <c r="D38" s="14">
+        <v>60</v>
+      </c>
+      <c r="E38" s="14">
+        <v>30</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>60</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>630</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>810</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B39" s="14">
+        <v>420</v>
+      </c>
+      <c r="C39" s="14">
+        <v>60</v>
+      </c>
+      <c r="D39" s="14">
+        <v>60</v>
+      </c>
+      <c r="E39" s="14">
+        <v>30</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>60</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>630</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>810</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B40" s="14">
+        <v>420</v>
+      </c>
+      <c r="C40" s="14">
+        <v>60</v>
+      </c>
+      <c r="D40" s="14">
+        <v>60</v>
+      </c>
+      <c r="E40" s="14">
+        <v>30</v>
+      </c>
+      <c r="F40" s="14">
+        <v>350</v>
+      </c>
+      <c r="G40" s="14">
+        <v>7</v>
+      </c>
+      <c r="H40" s="14">
+        <v>60</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>460</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B41" s="14">
+        <v>420</v>
+      </c>
+      <c r="C41" s="14">
+        <v>60</v>
+      </c>
+      <c r="D41" s="14">
+        <v>60</v>
+      </c>
+      <c r="E41" s="14">
+        <v>30</v>
+      </c>
+      <c r="F41" s="14">
+        <v>300</v>
+      </c>
+      <c r="G41" s="14">
+        <v>6</v>
+      </c>
+      <c r="H41" s="14">
+        <v>60</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B42" s="14">
+        <v>420</v>
+      </c>
+      <c r="C42" s="14">
+        <v>60</v>
+      </c>
+      <c r="D42" s="14">
+        <v>60</v>
+      </c>
+      <c r="E42" s="14">
+        <v>30</v>
+      </c>
+      <c r="F42" s="14">
+        <v>350</v>
+      </c>
+      <c r="G42" s="14">
+        <v>7</v>
+      </c>
+      <c r="H42" s="14">
+        <v>60</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>460</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" s="13"/>
